--- a/data/publikace.xlsx
+++ b/data/publikace.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jarom\Documents\GitHub\jfronc.cz\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BEE5BC-04D0-45C4-A77B-91E1FBF27FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA10525-C3BF-459A-BCDE-06EF01F229FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6FCB930-9EF3-4AF5-902E-F9B54FCB8C2A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A6FCB930-9EF3-4AF5-902E-F9B54FCB8C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="publikace" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="107">
   <si>
     <t>Item Type</t>
   </si>
@@ -317,6 +317,30 @@
   </si>
   <si>
     <t>https://www.ilaw.cas.cz/casopisy-a-knihy/casopisy/casopis-pravnik/archiv/2021/2021-3.html?a=3561</t>
+  </si>
+  <si>
+    <t>Stavební zákon. Komentář</t>
+  </si>
+  <si>
+    <t>978-80-7699-039-5</t>
+  </si>
+  <si>
+    <t>https://www.beck.cz/stavebni-zakon-komentar-2-svazky</t>
+  </si>
+  <si>
+    <t>C. H. Beck</t>
+  </si>
+  <si>
+    <t>https://app.beck-online.cz/bo/document-view.seam?documentId=nnptembsgvpwk5tlgmzq&amp;tocid=nnptembsgvpwk5tlgmzq</t>
+  </si>
+  <si>
+    <t>Fronc, Jaromír, Burda, Daniel</t>
+  </si>
+  <si>
+    <t>Komentář k § 2, 3, 145, 149, 153, 154, 334b a 335</t>
+  </si>
+  <si>
+    <t>Bursíková, L., Korbel, F., Černý, P., Lachmann, M., Roztočil, A., Bohadlo, D. a kol</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631FB780-6AFF-4288-ADD9-3288FF02E2D7}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.109375" customWidth="1"/>
@@ -1268,36 +1292,42 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2">
-        <v>6</v>
-      </c>
-      <c r="N2" t="s">
-        <v>63</v>
+        <v>101</v>
+      </c>
+      <c r="K2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>2024</v>
@@ -1306,25 +1336,22 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -1332,19 +1359,22 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
         <v>41</v>
@@ -1353,39 +1383,39 @@
         <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B5">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="N5" t="s">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="I5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -1399,33 +1429,27 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>2022</v>
@@ -1434,25 +1458,28 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="J7">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1466,57 +1493,60 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L8" t="s">
         <v>36</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="s">
-        <v>85</v>
+        <v>40</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1530,22 +1560,22 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1559,27 +1589,27 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
       </c>
       <c r="N11" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>2021</v>
@@ -1588,56 +1618,56 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
-      </c>
-      <c r="K12" t="s">
-        <v>70</v>
-      </c>
-      <c r="L12" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B13">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-      <c r="N13" t="s">
-        <v>56</v>
+        <v>97</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>2020</v>
@@ -1646,25 +1676,22 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
       </c>
       <c r="I14" t="s">
-        <v>89</v>
-      </c>
-      <c r="K14" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="J14">
+        <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1672,19 +1699,19 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s">
         <v>41</v>
@@ -1695,8 +1722,8 @@
       <c r="M15" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>88</v>
+      <c r="N15" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1704,31 +1731,31 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="L16" t="s">
         <v>36</v>
       </c>
       <c r="M16" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1742,13 +1769,13 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="s">
         <v>79</v>
@@ -1757,23 +1784,56 @@
         <v>36</v>
       </c>
       <c r="M17" t="s">
+        <v>42</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18">
+        <v>2018</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K18" t="s">
+        <v>79</v>
+      </c>
+      <c r="L18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M18" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O11">
-    <sortCondition descending="1" ref="B1:B11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O12">
+    <sortCondition descending="1" ref="B1:B12"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="N15" r:id="rId1" location="page=19" xr:uid="{F3D6A464-8709-4C70-A654-AAB6DF80C124}"/>
-    <hyperlink ref="N17" r:id="rId2" location="page=28" xr:uid="{9DB26DD3-7EDF-4B85-A083-BDDA15B3652F}"/>
-    <hyperlink ref="N16" r:id="rId3" location="page=31" xr:uid="{A2D4E3CD-DC51-4A86-84B3-32AE8CDCD9AF}"/>
-    <hyperlink ref="N8" r:id="rId4" location="page=99" xr:uid="{11EA39AE-735B-4DA9-90B2-73B8162222CD}"/>
-    <hyperlink ref="N4" r:id="rId5" location="page=63" xr:uid="{82DED146-3338-4385-9FFC-1E25F60D880D}"/>
+    <hyperlink ref="N16" r:id="rId1" location="page=19" xr:uid="{F3D6A464-8709-4C70-A654-AAB6DF80C124}"/>
+    <hyperlink ref="N18" r:id="rId2" location="page=28" xr:uid="{9DB26DD3-7EDF-4B85-A083-BDDA15B3652F}"/>
+    <hyperlink ref="N17" r:id="rId3" location="page=31" xr:uid="{A2D4E3CD-DC51-4A86-84B3-32AE8CDCD9AF}"/>
+    <hyperlink ref="N9" r:id="rId4" location="page=99" xr:uid="{11EA39AE-735B-4DA9-90B2-73B8162222CD}"/>
+    <hyperlink ref="N5" r:id="rId5" location="page=63" xr:uid="{82DED146-3338-4385-9FFC-1E25F60D880D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data/publikace.xlsx
+++ b/data/publikace.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jarom\Documents\GitHub\jfronc.cz\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA10525-C3BF-459A-BCDE-06EF01F229FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067205B2-3F47-4120-93E6-0E260F23FDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A6FCB930-9EF3-4AF5-902E-F9B54FCB8C2A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A6FCB930-9EF3-4AF5-902E-F9B54FCB8C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="publikace" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="112">
   <si>
     <t>Item Type</t>
   </si>
@@ -341,6 +341,21 @@
   </si>
   <si>
     <t>Bursíková, L., Korbel, F., Černý, P., Lachmann, M., Roztočil, A., Bohadlo, D. a kol</t>
+  </si>
+  <si>
+    <t>Difúzní přezkum právních předpisů</t>
+  </si>
+  <si>
+    <t>https://www.wintr.cz/images/samosprava.pdf#page=40</t>
+  </si>
+  <si>
+    <t>https://www.beck.cz/difuzni-prezkum-pravnich-predpisu</t>
+  </si>
+  <si>
+    <t>978-80-7400-996-9</t>
+  </si>
+  <si>
+    <t>book</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{631FB780-6AFF-4288-ADD9-3288FF02E2D7}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.109375" customWidth="1"/>
@@ -1292,71 +1307,68 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K2" t="s">
         <v>102</v>
       </c>
       <c r="L2" t="s">
         <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>99</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="N3" t="s">
-        <v>63</v>
+        <v>101</v>
+      </c>
+      <c r="K3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>2024</v>
@@ -1365,25 +1377,22 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s">
-        <v>51</v>
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -1391,19 +1400,22 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
         <v>41</v>
@@ -1412,39 +1424,42 @@
         <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B6">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="N6" t="s">
-        <v>81</v>
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1458,33 +1473,27 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="J7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>2022</v>
@@ -1493,25 +1502,28 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1525,57 +1537,60 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
-        <v>85</v>
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1589,22 +1604,22 @@
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1618,27 +1633,27 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" t="s">
-        <v>46</v>
+        <v>29</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
       </c>
       <c r="N12" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>2021</v>
@@ -1647,56 +1662,56 @@
         <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" t="s">
-        <v>70</v>
-      </c>
-      <c r="L13" t="s">
-        <v>36</v>
-      </c>
-      <c r="M13" t="s">
-        <v>68</v>
+        <v>60</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B14">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C14" t="s">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14">
-        <v>7</v>
-      </c>
-      <c r="N14" t="s">
-        <v>56</v>
+        <v>97</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B15">
         <v>2020</v>
@@ -1705,25 +1720,22 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>53</v>
+      </c>
+      <c r="H15" t="s">
+        <v>57</v>
       </c>
       <c r="I15" t="s">
-        <v>89</v>
-      </c>
-      <c r="K15" t="s">
-        <v>41</v>
-      </c>
-      <c r="L15" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="J15">
+        <v>7</v>
       </c>
       <c r="N15" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1731,19 +1743,19 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s">
         <v>41</v>
@@ -1754,8 +1766,8 @@
       <c r="M16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>88</v>
+      <c r="N16" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1763,31 +1775,31 @@
         <v>30</v>
       </c>
       <c r="B17">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="L17" t="s">
         <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1801,13 +1813,13 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s">
         <v>79</v>
@@ -1816,24 +1828,57 @@
         <v>36</v>
       </c>
       <c r="M18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19">
+        <v>2018</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O12">
-    <sortCondition descending="1" ref="B1:B12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:O13">
+    <sortCondition descending="1" ref="B1:B13"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="N16" r:id="rId1" location="page=19" xr:uid="{F3D6A464-8709-4C70-A654-AAB6DF80C124}"/>
-    <hyperlink ref="N18" r:id="rId2" location="page=28" xr:uid="{9DB26DD3-7EDF-4B85-A083-BDDA15B3652F}"/>
-    <hyperlink ref="N17" r:id="rId3" location="page=31" xr:uid="{A2D4E3CD-DC51-4A86-84B3-32AE8CDCD9AF}"/>
-    <hyperlink ref="N9" r:id="rId4" location="page=99" xr:uid="{11EA39AE-735B-4DA9-90B2-73B8162222CD}"/>
-    <hyperlink ref="N5" r:id="rId5" location="page=63" xr:uid="{82DED146-3338-4385-9FFC-1E25F60D880D}"/>
+    <hyperlink ref="N17" r:id="rId1" location="page=19" xr:uid="{F3D6A464-8709-4C70-A654-AAB6DF80C124}"/>
+    <hyperlink ref="N19" r:id="rId2" location="page=28" xr:uid="{9DB26DD3-7EDF-4B85-A083-BDDA15B3652F}"/>
+    <hyperlink ref="N18" r:id="rId3" location="page=31" xr:uid="{A2D4E3CD-DC51-4A86-84B3-32AE8CDCD9AF}"/>
+    <hyperlink ref="N10" r:id="rId4" location="page=99" xr:uid="{11EA39AE-735B-4DA9-90B2-73B8162222CD}"/>
+    <hyperlink ref="N6" r:id="rId5" location="page=63" xr:uid="{82DED146-3338-4385-9FFC-1E25F60D880D}"/>
+    <hyperlink ref="N5" r:id="rId6" location="page=40" xr:uid="{D3F0D49F-ED3C-4465-8286-7606800D479B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>